--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:12</t>
+          <t>2026-05-04 18:27</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:27</t>
+          <t>2026-05-05 12:56</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trip_Detail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$W$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W109"/>
+  <dimension ref="A1:Z109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -510,8 +510,11 @@
     <col width="24" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -529,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 12:56</t>
+          <t>2026-05-05 14:39</t>
         </is>
       </c>
     </row>
@@ -557,6 +560,9 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -666,10 +672,25 @@
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
+          <t>Trip_rate_baht</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Downtime_50_baht</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Downtime_100_baht</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
           <t>Nw_outbound50_baht</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>Return_manual_baht</t>
         </is>
@@ -748,9 +769,18 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -827,9 +857,18 @@
         <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -906,9 +945,18 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -985,9 +1033,18 @@
         <v>1</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1064,9 +1121,18 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1147,9 +1213,18 @@
         <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1226,9 +1301,18 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1305,9 +1389,18 @@
         <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1384,9 +1477,18 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W13" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,9 +1565,18 @@
         <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W14" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1542,9 +1653,18 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1621,9 +1741,18 @@
         <v>1</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1700,9 +1829,18 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1779,9 +1917,18 @@
         <v>1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W18" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1858,9 +2005,18 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W19" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1937,9 +2093,18 @@
         <v>1</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2016,9 +2181,18 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2095,9 +2269,18 @@
         <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W22" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2174,9 +2357,18 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W23" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2253,9 +2445,18 @@
         <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W24" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2332,9 +2533,18 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W25" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2411,9 +2621,18 @@
         <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2490,9 +2709,18 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2569,9 +2797,18 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2648,9 +2885,18 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W29" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2727,9 +2973,18 @@
         <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W30" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2806,9 +3061,18 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2885,9 +3149,18 @@
         <v>1</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W32" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2964,9 +3237,18 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3043,9 +3325,18 @@
         <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3122,9 +3413,18 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3205,9 +3505,18 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W36" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3284,9 +3593,18 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3363,9 +3681,18 @@
         <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3442,9 +3769,18 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3521,9 +3857,18 @@
         <v>1</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3600,9 +3945,18 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3679,9 +4033,18 @@
         <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W42" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3758,9 +4121,18 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W43" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3837,9 +4209,18 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3916,9 +4297,18 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3995,9 +4385,18 @@
         <v>1</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W46" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4074,9 +4473,18 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4153,9 +4561,18 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4232,9 +4649,18 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4311,9 +4737,18 @@
         <v>1</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W50" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4390,9 +4825,18 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4469,9 +4913,18 @@
         <v>1</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4552,9 +5005,18 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W53" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4631,9 +5093,18 @@
         <v>1</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4710,9 +5181,18 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W55" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4789,9 +5269,18 @@
         <v>1</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4868,9 +5357,18 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4947,9 +5445,18 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5026,9 +5533,18 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5105,9 +5621,18 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5184,9 +5709,18 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5263,9 +5797,18 @@
         <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W62" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5342,9 +5885,18 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5425,9 +5977,18 @@
         <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5504,9 +6065,18 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5583,9 +6153,18 @@
         <v>1</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5662,9 +6241,18 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5741,9 +6329,18 @@
         <v>1</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5820,9 +6417,18 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5903,9 +6509,18 @@
         <v>1</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5982,9 +6597,18 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6061,9 +6685,18 @@
         <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6140,9 +6773,18 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6219,9 +6861,18 @@
         <v>1</v>
       </c>
       <c r="V74" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W74" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6298,9 +6949,18 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6377,9 +7037,18 @@
         <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6456,9 +7125,18 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6539,9 +7217,18 @@
         <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6618,9 +7305,18 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6697,9 +7393,18 @@
         <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6780,9 +7485,18 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6859,9 +7573,18 @@
         <v>1</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6938,9 +7661,18 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7021,9 +7753,18 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="Y84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7100,9 +7841,18 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="Y85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7179,9 +7929,18 @@
         <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="Y86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7258,9 +8017,18 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W87" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7337,9 +8105,18 @@
         <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W88" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7416,9 +8193,18 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7495,9 +8281,18 @@
         <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W90" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7574,9 +8369,18 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W91" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7653,9 +8457,18 @@
         <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W92" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="10" t="n">
         <v>7500</v>
       </c>
     </row>
@@ -7732,9 +8545,18 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W93" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7811,9 +8633,18 @@
         <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="10" t="n">
         <v>3750</v>
       </c>
-      <c r="W94" s="10" t="n">
+      <c r="Z94" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7890,9 +8721,18 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W95" s="7" t="n">
         <v>3750</v>
       </c>
-      <c r="W95" s="7" t="n">
+      <c r="X95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z95" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7969,9 +8809,18 @@
         <v>1</v>
       </c>
       <c r="V96" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W96" s="10" t="n">
         <v>3750</v>
       </c>
-      <c r="W96" s="10" t="n">
+      <c r="X96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z96" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8048,9 +8897,18 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8127,9 +8985,18 @@
         <v>1</v>
       </c>
       <c r="V98" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8206,9 +9073,18 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8285,9 +9161,18 @@
         <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8364,9 +9249,18 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8447,9 +9341,18 @@
         <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W102" s="10" t="n">
         <v>3750</v>
       </c>
-      <c r="W102" s="10" t="n">
+      <c r="X102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z102" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8526,9 +9429,18 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W103" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8605,9 +9517,18 @@
         <v>1</v>
       </c>
       <c r="V104" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W104" s="10" t="n">
         <v>3750</v>
       </c>
-      <c r="W104" s="10" t="n">
+      <c r="X104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z104" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8684,9 +9605,18 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W105" s="7" t="n">
         <v>3750</v>
       </c>
-      <c r="W105" s="7" t="n">
+      <c r="X105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z105" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8763,9 +9693,18 @@
         <v>1</v>
       </c>
       <c r="V106" s="10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W106" s="10" t="n">
         <v>3750</v>
       </c>
-      <c r="W106" s="10" t="n">
+      <c r="X106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z106" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8842,9 +9781,18 @@
         <v>1</v>
       </c>
       <c r="V107" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="W107" s="7" t="n">
         <v>3750</v>
       </c>
-      <c r="W107" s="7" t="n">
+      <c r="X107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z107" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8921,9 +9869,18 @@
         <v>1</v>
       </c>
       <c r="V108" s="10" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W108" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9000,16 +9957,25 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="W109" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="X109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="7" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:W109"/>
+  <autoFilter ref="A4:Z109"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A1:Z1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
